--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>122243192</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.0520000010728836</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.0450000017881393</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.0439999997615814</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -62897,7 +62897,7 @@
         <v>0.0520000010728836</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.0450000017881393</v>
+        <v>0.0439999997615814</v>
       </c>
       <c r="E2719" t="n">
         <v>0.0500000007450581</v>
@@ -62906,6 +62906,29 @@
         <v>0.0439999997615814</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>85678374</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.0452999994158745</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.0399000011384487</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.0423000007867813</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.0447999984025955</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>40374902</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.0467999987304211</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.0434000007808208</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.0450000017881393</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.0432999990880489</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -62943,7 +62943,7 @@
         <v>0.0467999987304211</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.0434000007808208</v>
+        <v>0.0432999990880489</v>
       </c>
       <c r="E2721" t="n">
         <v>0.0450000017881393</v>
@@ -62952,6 +62952,29 @@
         <v>0.0432999990880489</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>46094770</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.0478999987244606</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.0434999987483025</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.0439999997615814</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.046900000423193</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>118466035</v>
+        <v>60204550</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.0408000014722347</v>
+        <v>0.0373999997973442</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.0368000008165836</v>
+        <v>0.0335999988019466</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.0381000004708767</v>
+        <v>0.0344999991357327</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.0395000018179417</v>
+        <v>0.0373999997973442</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>74955701</v>
+        <v>118466035</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.0428999997675419</v>
+        <v>0.0408000014722347</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.0386000014841557</v>
+        <v>0.0368000008165836</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.0399000011384487</v>
+        <v>0.0381000004708767</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.0412000007927418</v>
+        <v>0.0395000018179417</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>77737842</v>
+        <v>74955701</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.0450000017881393</v>
+        <v>0.0428999997675419</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.0414999984204769</v>
+        <v>0.0386000014841557</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.0423000007867813</v>
+        <v>0.0399000011384487</v>
       </c>
       <c r="F2717" t="n">
-        <v>0.0438000001013279</v>
+        <v>0.0412000007927418</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>83356025</v>
+        <v>77737842</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.0485999993979931</v>
+        <v>0.0450000017881393</v>
       </c>
       <c r="D2718" t="n">
         <v>0.0414999984204769</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.0447000004351139</v>
+        <v>0.0423000007867813</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.0485000014305115</v>
+        <v>0.0438000001013279</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>122243192</v>
+        <v>83356025</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.0520000010728836</v>
+        <v>0.0485999993979931</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.0439999997615814</v>
+        <v>0.0414999984204769</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.0500000007450581</v>
+        <v>0.0447000004351139</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.0439999997615814</v>
+        <v>0.0485000014305115</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>85678374</v>
+        <v>122243192</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.0452999994158745</v>
+        <v>0.0520000010728836</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.0399000011384487</v>
+        <v>0.0439999997615814</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.0423000007867813</v>
+        <v>0.0500000007450581</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.0447999984025955</v>
+        <v>0.0439999997615814</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>40374902</v>
+        <v>85678374</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.0467999987304211</v>
+        <v>0.0452999994158745</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.0432999990880489</v>
+        <v>0.0399000011384487</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.0450000017881393</v>
+        <v>0.0423000007867813</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.0432999990880489</v>
+        <v>0.0447999984025955</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>46094770</v>
+        <v>40374902</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.0478999987244606</v>
+        <v>0.0467999987304211</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.0434999987483025</v>
+        <v>0.0432999990880489</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.0439999997615814</v>
+        <v>0.0450000017881393</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.046900000423193</v>
+        <v>0.0432999990880489</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>95081245</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.0502000004053116</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.0450000017881393</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.0471000000834465</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.0461000017821789</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>70461242</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.0513000003993511</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.0472000017762184</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.0494999997317791</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.0463000014424324</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.0463000014424324</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -71236,7 +71236,7 @@
         <v>0.0513000003993511</v>
       </c>
       <c r="D2726" t="n">
-        <v>0.0472000017762184</v>
+        <v>0.0463000014424324</v>
       </c>
       <c r="E2726" t="n">
         <v>0.0494999997317791</v>
@@ -71248,6 +71248,32 @@
         <v>0.0463000014424324</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>35127174</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.0480999983847141</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.0445000007748604</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.0461000017821789</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.0456999987363815</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.0456999987363815</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>28055109</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.0465000011026859</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.0434999987483025</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.0456999987363815</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.0447000004351139</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.0447000004351139</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -71303,6 +71303,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>13704879</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.0452000014483929</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.0430999994277954</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.0450000017881393</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.0439000017940998</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.0439000017940998</v>
+      </c>
+      <c r="H2729" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>30787471</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.0461000017821789</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.0421000011265278</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.0423999987542629</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.0447999984025955</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.0447999984025955</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.0438000001013279</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.0410000011324883</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>41298775</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.0428000018000603</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.0384000018239021</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.0403999984264374</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.0403999984264374</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.0384999997913837</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>54842762</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.0346000008285046</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.0373000018298626</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.0373000018298626</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.0348999984562397</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>27913620</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.0362999998033047</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.0333000011742115</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.0353999994695187</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.0353999994695187</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.034000001847744</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>26896265</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.0364000014960766</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.0326999984681606</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.0333999991416931</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>33301245</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.0370000004768372</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.0342999994754791</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.0359000004827976</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.034400001168251</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -71667,6 +71667,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>28189337</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.0346999987959862</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.032600000500679</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.0346000008285046</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.0337999984622002</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.0337999984622002</v>
+      </c>
+      <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -71672,7 +71672,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2743" t="n">
-        <v>28189337</v>
+        <v>28336040</v>
       </c>
       <c r="C2743" t="n">
         <v>0.0346999987959862</v>
@@ -71690,6 +71690,32 @@
         <v>0.0337999984622002</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>71037262</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.0329999998211861</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.0249000005424023</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.0329999998211861</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.0229000002145767</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.0132999997586012</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.0229000002145767</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.0229000002145767</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>37235527</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.025000000372529</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.0249000005424023</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.0249000005424023</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>41454171</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.0253999996930361</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.025900000706315</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.022299999371171</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.0225000008940697</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.0225000008940697</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>32068810</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>19906944</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80055,7 +80055,7 @@
         <v>0.0230000000447035</v>
       </c>
       <c r="E2748" t="n">
-        <v>0.0201999992132187</v>
+        <v>0.0199999995529652</v>
       </c>
       <c r="F2748" t="n">
         <v>0.0199999995529652</v>
@@ -80067,6 +80067,35 @@
         <v>19906944</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.0157999992370605</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>44480317</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.0195000004023314</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>26501690</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80128,6 +80128,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.0197999998927116</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.017400000244379</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>28324119</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80139,7 +80139,7 @@
         <v>0.0179999992251396</v>
       </c>
       <c r="D2751" t="n">
-        <v>0.0197999998927116</v>
+        <v>0.0199999995529652</v>
       </c>
       <c r="E2751" t="n">
         <v>0.017400000244379</v>
@@ -80154,6 +80154,35 @@
         <v>28324119</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.0187999997287989</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.0205000005662441</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.0181000009179115</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>19906224</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80168,7 +80168,7 @@
         <v>0.0187999997287989</v>
       </c>
       <c r="D2752" t="n">
-        <v>0.0205000005662441</v>
+        <v>0.0206000003963709</v>
       </c>
       <c r="E2752" t="n">
         <v>0.0181000009179115</v>
@@ -80183,6 +80183,35 @@
         <v>19906224</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.0220999997109175</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.0207000002264977</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.0207000002264977</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>18823061</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RN.MI.xlsx
+++ b/data/RN.MI.xlsx
@@ -80215,6 +80215,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>0.0207000002264977</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>0.0208000000566244</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>0.0188999995589256</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>15738972</v>
+      </c>
+      <c r="I2754" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
